--- a/artfynd/A 3382-2023 artfynd.xlsx
+++ b/artfynd/A 3382-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3382-2023 artfynd.xlsx
+++ b/artfynd/A 3382-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3158,126 +3158,6 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>113349341</v>
-      </c>
-      <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Vegalla, Ög</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>570108</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6464064</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Åtvidaberg</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Yxnerum</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>E-Åtv-0250</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Många växtplatser i närheten.</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
